--- a/Raw_data/Control_Patent.xlsx
+++ b/Raw_data/Control_Patent.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aksha\Downloads\Akshaya\Professional\CBAM_Research\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aksha\Downloads\Akshaya\Professional\CBAM_Research\Raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EAC1D6F-B1F4-4213-98B0-C8E9592755F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B1DFD6-AEFE-4B7A-BDB9-6810544FBC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FD5766FD-A9AF-4D7D-B8B3-8D5B05AC1000}"/>
   </bookViews>
@@ -438,6 +438,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7395902F-14E9-459E-915C-0D3733946C2D}">
   <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34.33203125" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
